--- a/output/completed_orders.xlsx
+++ b/output/completed_orders.xlsx
@@ -554,9 +554,7 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>45</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -601,7 +599,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>275.5</v>
       </c>
     </row>
     <row r="9">

--- a/output/completed_orders.xlsx
+++ b/output/completed_orders.xlsx
@@ -554,7 +554,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
